--- a/proposal/chuangzhihui-30-events-waic-cj-fuse.xlsx
+++ b/proposal/chuangzhihui-30-events-waic-cj-fuse.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -3285,7 +3285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3307,180 +3307,144 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定稿说明</t>
+          <t>视觉</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>多版优胜劣汰合并；紫金主题；Excel0804场次为准</t>
+          <t>皇家紫金主题（深紫渐变+蓝紫点缀+香槟金）</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>视觉</t>
+          <t>主体运营范围</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>皇家紫金主题（深紫渐变+蓝紫点缀+香槟金）</t>
+          <t>上海市云计算创新基地（国家级孵化器）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>主体运营范围</t>
+          <t>学术支持</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>上海市云计算创新基地（国家级孵化器）</t>
+          <t>复旦大学住房政策研究中心</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>学术支持</t>
+          <t>载体支持</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>复旦大学住房政策研究中心</t>
+          <t>杨浦区科技企业联合会、科技企业服务中心</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>载体支持</t>
+          <t>执行带客</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>杨浦区科技企业联合会、科技企业服务中心</t>
+          <t>同浦汇</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>执行带客</t>
+          <t>销售</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>同浦汇</t>
+          <t>园区负责销售部分</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>人数</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>园区负责销售部分</t>
+          <t>每场≤30人；全年约600人次+</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>人数</t>
+          <t>负责人</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>每场≤30人；全年约600人次+</t>
+          <t>≤30%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>负责人</t>
+          <t>双会</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>WAIC→3F；ChinaJoy→5F；具身/AIGC叠加</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>双会</t>
+          <t>出海/领事</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>WAIC→3F；ChinaJoy→5F；具身/AIGC叠加</t>
+          <t>另议另计价；到访≠挂牌</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>最新时点</t>
+          <t>租金</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026.08：WAIC已闭幕、ChinaJoy刚结束，进入承接期</t>
+          <t>3.3元/㎡/天；不做对赌；免租期1–3个月面议</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>出海/领事</t>
+          <t>付款</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>另议另计价；到访≠挂牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>租金</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>3.3元/㎡/天；不做对赌；免租期1–3个月面议</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>付款</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
           <t>签约后7日50%；四季各10%；年终10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>剔除</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>关联度核验表、千人级承诺、潮玩产业集群旧场、租赁对赌主叙事</t>
         </is>
       </c>
     </row>
